--- a/outputs/daily/hr_rankings_2026-08-24_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-24_remaining.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18392,7 +18392,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -22592,7 +22592,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -29876,7 +29876,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30996,7 +30996,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -31560,7 +31560,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -32676,7 +32676,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -33792,7 +33792,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -34072,7 +34072,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
